--- a/Data/Mock Data.xlsx
+++ b/Data/Mock Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8ad9e7a99cd65eb1/เอกสาร/Thesis Proposal/15 Data Collection_8 June 68 onwards/5 data from survey/4 ML data/3 Prototype/SMEs_Fin_Health_Check_v2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_F25DC773A252ABDACC10483EA99947EE5BDE5914" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91B2F102-3412-446D-934B-79A38254797F}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="11_F25DC773A252ABDACC10483EA99947EE5BDE5914" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8246D9FE-6E91-47B1-BDB6-BF6D6D984C0D}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11596" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="159">
   <si>
     <t>ID</t>
   </si>
@@ -493,6 +493,15 @@
   </si>
   <si>
     <t>J</t>
+  </si>
+  <si>
+    <t>Avg3Y_NI_Ratio</t>
+  </si>
+  <si>
+    <t>SAV_PDPA_x_PRC_CFW</t>
+  </si>
+  <si>
+    <t>PRC_CFW_x_Avg3Y_NI</t>
   </si>
 </sst>
 </file>
@@ -629,7 +638,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -685,6 +694,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -970,10 +980,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:EM11"/>
+  <dimension ref="A1:EP11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="144" max="144" width="13.796875" customWidth="1"/>
+    <col min="145" max="145" width="19.53125" bestFit="1" customWidth="1"/>
+    <col min="146" max="146" width="18.73046875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:143" s="16" customFormat="1" ht="21" x14ac:dyDescent="0.95">
+    <row r="1" spans="1:146" s="16" customFormat="1" ht="21" x14ac:dyDescent="0.95">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1403,8 +1418,17 @@
       <c r="EM1" s="14" t="s">
         <v>142</v>
       </c>
+      <c r="EN1" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="EO1" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="EP1" s="21" t="s">
+        <v>158</v>
+      </c>
     </row>
-    <row r="2" spans="1:143" s="20" customFormat="1" ht="21" x14ac:dyDescent="0.95">
+    <row r="2" spans="1:146" s="20" customFormat="1" ht="21" x14ac:dyDescent="0.95">
       <c r="A2" s="17">
         <v>103</v>
       </c>
@@ -1726,8 +1750,17 @@
       <c r="EM2" s="16">
         <v>0</v>
       </c>
+      <c r="EN2" s="16">
+        <v>0</v>
+      </c>
+      <c r="EO2" s="16">
+        <v>0</v>
+      </c>
+      <c r="EP2" s="16">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:143" s="20" customFormat="1" ht="21" x14ac:dyDescent="0.95">
+    <row r="3" spans="1:146" s="20" customFormat="1" ht="21" x14ac:dyDescent="0.95">
       <c r="A3" s="17">
         <v>104</v>
       </c>
@@ -2118,7 +2151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:143" s="20" customFormat="1" ht="21" x14ac:dyDescent="0.95">
+    <row r="4" spans="1:146" s="20" customFormat="1" ht="21" x14ac:dyDescent="0.95">
       <c r="A4" s="17">
         <v>105</v>
       </c>
@@ -2539,7 +2572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:143" s="20" customFormat="1" ht="21" x14ac:dyDescent="0.95">
+    <row r="5" spans="1:146" s="20" customFormat="1" ht="21" x14ac:dyDescent="0.95">
       <c r="A5" s="17">
         <v>106</v>
       </c>
@@ -2848,7 +2881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:143" s="20" customFormat="1" ht="21" x14ac:dyDescent="0.95">
+    <row r="6" spans="1:146" s="20" customFormat="1" ht="21" x14ac:dyDescent="0.95">
       <c r="A6" s="17">
         <v>107</v>
       </c>
@@ -3251,7 +3284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:143" s="20" customFormat="1" ht="21" x14ac:dyDescent="0.95">
+    <row r="7" spans="1:146" s="20" customFormat="1" ht="21" x14ac:dyDescent="0.95">
       <c r="A7" s="17">
         <v>108</v>
       </c>
@@ -3522,7 +3555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:143" s="20" customFormat="1" ht="21" x14ac:dyDescent="0.95">
+    <row r="8" spans="1:146" s="20" customFormat="1" ht="21" x14ac:dyDescent="0.95">
       <c r="A8" s="17">
         <v>109</v>
       </c>
@@ -3793,7 +3826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:143" s="20" customFormat="1" ht="21" x14ac:dyDescent="0.95">
+    <row r="9" spans="1:146" s="20" customFormat="1" ht="21" x14ac:dyDescent="0.95">
       <c r="A9" s="17">
         <v>110</v>
       </c>
@@ -4064,7 +4097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:143" s="20" customFormat="1" ht="21" x14ac:dyDescent="0.95">
+    <row r="10" spans="1:146" s="20" customFormat="1" ht="21" x14ac:dyDescent="0.95">
       <c r="A10" s="17">
         <v>111</v>
       </c>
@@ -4335,7 +4368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:143" s="20" customFormat="1" ht="21" x14ac:dyDescent="0.95">
+    <row r="11" spans="1:146" s="20" customFormat="1" ht="21" x14ac:dyDescent="0.95">
       <c r="A11" s="17">
         <v>112</v>
       </c>
